--- a/data/merged/2026-09-09/MERGED_UK_Stick-Vacuum_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_UK_Stick-Vacuum_2026-09-09.xlsx
@@ -6439,13 +6439,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6483,13 +6483,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6527,13 +6527,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7050,50 +7050,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7419,7 +7375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -15896,40 +15852,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0F9YPP9C3</t>
+          <t>B0DJ71KLJG</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Levoit</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0F9YPP9C3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0DJ71KLJG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Shark Disposable Hard Floor Vacuum and Mop Pad VACMOP Refill 16 Pack, WhitesWhite 1304HK200UK</t>
+          <t>Levoit Cordless Vacuum Cleaner, Anti-Hair Wrap, Lightweights100,000 RPM Motor, 99.7% Hard Floor Clean, Up to 50 Min Runtime</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DJ71KLJG?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41a3F1M66OL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0F9YPP9C3</t>
+          <t>B0DJ71KLJG</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -15943,13 +15899,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>1187</v>
+        <v>8468</v>
       </c>
       <c r="P37" s="15">
-        <v>-223</v>
+        <v>10100</v>
       </c>
       <c r="Q37" s="16">
-        <v>-0.23</v>
+        <v>0.54</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -15958,61 +15914,61 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>2107</v>
+        <v>355</v>
       </c>
       <c r="U37" s="16">
-        <v>0.01</v>
+        <v>2.02</v>
       </c>
       <c r="V37" s="15">
-        <v>31584</v>
+        <v>31350</v>
       </c>
       <c r="W37" s="15" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X37" s="15">
-        <v>29980</v>
+        <v>8831</v>
       </c>
       <c r="Y37" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z37" s="20">
-        <v>12.49</v>
+        <v>88.31</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="15"/>
       <c r="AD37" s="19">
-        <v>186</v>
+        <v>9877</v>
       </c>
       <c r="AE37" s="15">
-        <v>14</v>
+        <v>9534</v>
       </c>
       <c r="AF37" s="21">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG37" s="22">
-        <v>0.0066</v>
+        <v>0</v>
       </c>
       <c r="AH37" s="20">
-        <v>3.2</v>
+        <v>5.28</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.79</v>
+        <v>0.94</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>469</v>
+        <v>709</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
@@ -16023,10 +15979,10 @@
       <c r="AO37" s="13"/>
       <c r="AP37"/>
       <c r="AQ37" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR37" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
@@ -16071,47 +16027,43 @@
       </c>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>550 g</t>
+          <t>2.79 kg</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>2.79 kg</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>9.9 x 15.5 x 25.4 cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="23" t="inlineStr">
-        <is>
-          <t>9.90 x 15.50 x 25.40 cm</t>
-        </is>
-      </c>
+          <t>110L x 19.5W x 25H centimetres</t>
+        </is>
+      </c>
+      <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>550 g</t>
+          <t>4.76 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>4.76 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>26 x 16 x 16 cm</t>
+          <t>45.2 x 33 x 19 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>26.00 x 16.00 x 16.00 cm</t>
+          <t>45.20 x 33.00 x 19.00 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16122,40 +16074,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0DJ71KLJG</t>
+          <t>B09SG94978</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Levoit</t>
+          <t>Tower</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0DJ71KLJG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09SG94978&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Levoit Cordless Vacuum Cleaner, Anti-Hair Wrap, Lightweights100,000 RPM Motor, 99.7% Hard Floor Clean, Up to 50 Min Runtime</t>
+          <t>Tower Pro Corded 3-in-1 Vacuum Cleaner with Cyclonic Suction, Built-in HEPA 13 Filter and Detachable Handheld Mode, Black and</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DJ71KLJG?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09SG94978?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41a3F1M66OL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51U8DhXUrWL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0DJ71KLJG</t>
+          <t>B09SG94978</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -16169,13 +16121,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>8468</v>
+        <v>4062</v>
       </c>
       <c r="P38" s="15">
-        <v>10100</v>
+        <v>-962</v>
       </c>
       <c r="Q38" s="16">
-        <v>0.54</v>
+        <v>-0.31</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -16184,61 +16136,61 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>355</v>
+        <v>922</v>
       </c>
       <c r="U38" s="16">
-        <v>2.02</v>
+        <v>-0.23</v>
       </c>
       <c r="V38" s="15">
-        <v>31350</v>
+        <v>31256</v>
       </c>
       <c r="W38" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="X38" s="15">
-        <v>8831</v>
+        <v>13568</v>
       </c>
       <c r="Y38" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z38" s="20">
-        <v>88.31</v>
+        <v>28.25</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="15"/>
       <c r="AD38" s="19">
-        <v>9877</v>
+        <v>3482</v>
       </c>
       <c r="AE38" s="15">
-        <v>9534</v>
+        <v>39</v>
       </c>
       <c r="AF38" s="21">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AG38" s="22">
-        <v>0</v>
+        <v>0.042300000000000004</v>
       </c>
       <c r="AH38" s="20">
-        <v>5.28</v>
+        <v>3.59</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.94</v>
+        <v>0.89</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>709</v>
+        <v>238</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
@@ -16252,7 +16204,7 @@
         <v>10</v>
       </c>
       <c r="AR38" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
@@ -16268,11 +16220,7 @@
       <c r="AV38" s="14"/>
       <c r="AW38" s="13"/>
       <c r="AX38" s="13"/>
-      <c r="AY38" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY38" s="13"/>
       <c r="AZ38" s="13"/>
       <c r="BA38" s="13"/>
       <c r="BB38" s="13"/>
@@ -16290,50 +16238,50 @@
       <c r="BF38" s="13"/>
       <c r="BG38" s="13"/>
       <c r="BH38" s="14"/>
-      <c r="BI38" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI38" s="23"/>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>2.79 kg</t>
+          <t>1.46 kg</t>
         </is>
       </c>
       <c r="BK38" s="23" t="inlineStr">
         <is>
-          <t>2.79 kg</t>
+          <t>1.46 kg</t>
         </is>
       </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>110L x 19.5W x 25H centimetres</t>
-        </is>
-      </c>
-      <c r="BM38" s="23"/>
+          <t>10.2 x 8.3 x 42.5 cm</t>
+        </is>
+      </c>
+      <c r="BM38" s="23" t="inlineStr">
+        <is>
+          <t>10.20 x 8.30 x 42.50 cm</t>
+        </is>
+      </c>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>4.76 kg</t>
+          <t>2.59 kg</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>4.76 kg</t>
+          <t>2.59 kg</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>45.2 x 33 x 19 cm</t>
+          <t>42.3 x 25.1 x 17.6 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>45.20 x 33.00 x 19.00 cm</t>
+          <t>42.30 x 25.10 x 17.60 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16344,40 +16292,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B09SG94978</t>
+          <t>B0746H6J2R</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Tower</t>
+          <t>VonHaus</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09SG94978&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0746H6J2R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Tower Pro Corded 3-in-1 Vacuum Cleaner with Cyclonic Suction, Built-in HEPA 13 Filter and Detachable Handheld Mode, Black and</t>
+          <t>VonHaus Stick Vacuum Cleaner 800W 17000Pa Corded – 2 in 1 Upright &amp; Handheld Vacuum Cleaner with Lightweight Design, HEPA Fil</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09SG94978?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0746H6J2R?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51U8DhXUrWL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71O74t-35IL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B09SG94978</t>
+          <t>B0746H6J2R</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -16391,13 +16339,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>4062</v>
+        <v>6403</v>
       </c>
       <c r="P39" s="15">
-        <v>-962</v>
+        <v>-2878</v>
       </c>
       <c r="Q39" s="16">
-        <v>-0.31</v>
+        <v>-0.82</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16406,65 +16354,67 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>922</v>
+        <v>892</v>
       </c>
       <c r="U39" s="16">
-        <v>-0.23</v>
+        <v>0.36</v>
       </c>
       <c r="V39" s="15">
-        <v>31256</v>
+        <v>29427</v>
       </c>
       <c r="W39" s="15" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>800</t>
         </is>
       </c>
       <c r="X39" s="15">
-        <v>13568</v>
+        <v>29896</v>
       </c>
       <c r="Y39" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z39" s="20">
-        <v>28.25</v>
+        <v>32.99</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
-      <c r="AC39" s="15"/>
+      <c r="AC39" s="15">
+        <v>110</v>
+      </c>
       <c r="AD39" s="19">
-        <v>3482</v>
+        <v>4829</v>
       </c>
       <c r="AE39" s="15">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="AF39" s="21">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.042300000000000004</v>
+        <v>0.0381</v>
       </c>
       <c r="AH39" s="20">
-        <v>3.59</v>
+        <v>3.42</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2017-07-24</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>238</v>
+        <v>3333</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN39" s="13"/>
@@ -16474,23 +16424,39 @@
         <v>10</v>
       </c>
       <c r="AR39" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>VonHaus UK</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU39" s="13"/>
-      <c r="AV39" s="14"/>
-      <c r="AW39" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU39" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV39" s="14" t="inlineStr">
+        <is>
+          <t>SALFORD Manchester M3 7BF GB</t>
+        </is>
+      </c>
+      <c r="AW39" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6</t>
+        </is>
+      </c>
       <c r="AX39" s="13"/>
-      <c r="AY39" s="13"/>
+      <c r="AY39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
@@ -16508,45 +16474,49 @@
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
       <c r="BH39" s="14"/>
-      <c r="BI39" s="23"/>
+      <c r="BI39" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>1.46 kg</t>
+          <t>2.52 kg</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>1.46 kg</t>
+          <t>2.52 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>10.2 x 8.3 x 42.5 cm</t>
+          <t>23 x 14.5 x 132.2 cm</t>
         </is>
       </c>
       <c r="BM39" s="23" t="inlineStr">
         <is>
-          <t>10.20 x 8.30 x 42.50 cm</t>
+          <t>23.00 x 14.50 x 132.20 cm</t>
         </is>
       </c>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>2.59 kg</t>
+          <t>2.52 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>2.59 kg</t>
+          <t>2.52 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>42.3 x 25.1 x 17.6 cm</t>
+          <t>44.7 x 18.8 x 18 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>42.30 x 25.10 x 17.60 cm</t>
+          <t>44.70 x 18.80 x 18.00 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
@@ -16562,40 +16532,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0746H6J2R</t>
+          <t>B0GHKWY3KT</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>VonHaus</t>
+          <t>FAMIVAC</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0746H6J2R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0GHKWY3KT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>VonHaus Stick Vacuum Cleaner 800W 17000Pa Corded – 2 in 1 Upright &amp; Handheld Vacuum Cleaner with Lightweight Design, HEPA Fil</t>
+          <t>FAMIVAC Corded Vacuum Cleaner Powerful 65KPa, 7M Cord for Pet Hair CarpetsFV2 Hoover with Mattress Brush &amp; Anti Hair Wrap,</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0746H6J2R?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GHKWY3KT?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71O74t-35IL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71t+DWqwinL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0746H6J2R</t>
+          <t>B0GHKWY3KT</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -16609,13 +16579,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>6403</v>
+        <v>13791</v>
       </c>
       <c r="P40" s="15">
-        <v>-2878</v>
+        <v>7264</v>
       </c>
       <c r="Q40" s="16">
-        <v>-0.82</v>
+        <v>0.35</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -16624,67 +16594,65 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>52</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>892</v>
+        <v>326</v>
       </c>
       <c r="U40" s="16">
-        <v>0.36</v>
+        <v>-0.65</v>
       </c>
       <c r="V40" s="15">
-        <v>29427</v>
+        <v>29337</v>
       </c>
       <c r="W40" s="15" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X40" s="15">
-        <v>29896</v>
+        <v>10366</v>
       </c>
       <c r="Y40" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z40" s="20">
-        <v>32.99</v>
+        <v>63.73</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
-      <c r="AC40" s="15">
-        <v>110</v>
-      </c>
+      <c r="AC40" s="15"/>
       <c r="AD40" s="19">
-        <v>4829</v>
+        <v>679</v>
       </c>
       <c r="AE40" s="15">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="AF40" s="21">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AG40" s="22">
-        <v>0.0381</v>
+        <v>0.5215</v>
       </c>
       <c r="AH40" s="20">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2017-07-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>3333</v>
+        <v>204</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN40" s="13"/>
@@ -16698,35 +16666,19 @@
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>VonHaus UK</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU40" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV40" s="14" t="inlineStr">
-        <is>
-          <t>SALFORD Manchester M3 7BF GB</t>
-        </is>
-      </c>
-      <c r="AW40" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU40" s="13"/>
+      <c r="AV40" s="14"/>
+      <c r="AW40" s="13"/>
       <c r="AX40" s="13"/>
-      <c r="AY40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY40" s="13"/>
       <c r="AZ40" s="13"/>
       <c r="BA40" s="13"/>
       <c r="BB40" s="13"/>
@@ -16744,49 +16696,45 @@
       <c r="BF40" s="13"/>
       <c r="BG40" s="13"/>
       <c r="BH40" s="14"/>
-      <c r="BI40" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI40" s="23"/>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>2.52 kg</t>
+          <t>1.3 kg</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>2.52 kg</t>
+          <t>1.30 kg</t>
         </is>
       </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>23 x 14.5 x 132.2 cm</t>
+          <t>44 x 29 x 19 cm</t>
         </is>
       </c>
       <c r="BM40" s="23" t="inlineStr">
         <is>
-          <t>23.00 x 14.50 x 132.20 cm</t>
+          <t>44.00 x 29.00 x 19.00 cm</t>
         </is>
       </c>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>2.52 kg</t>
+          <t>3.41 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>2.52 kg</t>
+          <t>3.41 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>44.7 x 18.8 x 18 cm</t>
+          <t>44.3 x 29.2 x 19.1 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>44.70 x 18.80 x 18.00 cm</t>
+          <t>44.30 x 29.20 x 19.10 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
@@ -16802,40 +16750,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0GHKWY3KT</t>
+          <t>B09RMQ1XLL</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>FAMIVAC</t>
+          <t>VYTRONIX</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0GHKWY3KT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>FAMIVAC Corded Vacuum Cleaner Powerful 65KPa, 7M Cord for Pet Hair CarpetsFV2 Hoover with Mattress Brush &amp; Anti Hair Wrap,</t>
+          <t>VYTRONIX HSV3 Upright Vacuum CleanersLightweight 3-in-1 Compact Powerful Multifunction Corded Stick &amp; Handheld Vacuum | 600</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GHKWY3KT?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71t+DWqwinL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0GHKWY3KT</t>
+          <t>B09RMQ1XLL</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16849,13 +16797,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>13791</v>
+        <v>6112</v>
       </c>
       <c r="P41" s="15">
-        <v>7264</v>
+        <v>2094</v>
       </c>
       <c r="Q41" s="16">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16864,65 +16812,65 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>326</v>
+        <v>762</v>
       </c>
       <c r="U41" s="16">
-        <v>-0.65</v>
+        <v>0.41</v>
       </c>
       <c r="V41" s="15">
-        <v>29337</v>
+        <v>25138</v>
       </c>
       <c r="W41" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>600</t>
         </is>
       </c>
       <c r="X41" s="15">
-        <v>10366</v>
+        <v>19194</v>
       </c>
       <c r="Y41" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>63.73</v>
+        <v>32.99</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="15"/>
       <c r="AD41" s="19">
-        <v>679</v>
+        <v>4162</v>
       </c>
       <c r="AE41" s="15">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="AF41" s="21">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.5215</v>
+        <v>0.0105</v>
       </c>
       <c r="AH41" s="20">
-        <v>3.61</v>
+        <v>4.87</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>204</v>
+        <v>1665</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
@@ -16936,19 +16884,35 @@
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Vytronix</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU41" s="13"/>
-      <c r="AV41" s="14"/>
-      <c r="AW41" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU41" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV41" s="14" t="inlineStr">
+        <is>
+          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+        </is>
+      </c>
+      <c r="AW41" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+        </is>
+      </c>
       <c r="AX41" s="13"/>
-      <c r="AY41" s="13"/>
+      <c r="AY41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ41" s="13"/>
       <c r="BA41" s="13"/>
       <c r="BB41" s="13"/>
@@ -16957,59 +16921,59 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD41" s="13"/>
       <c r="BE41" s="13"/>
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
       <c r="BH41" s="14"/>
-      <c r="BI41" s="23"/>
+      <c r="BI41" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>1.3 kg</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>1.30 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>44 x 29 x 19 cm</t>
+          <t>31 x 11 x 21 cm</t>
         </is>
       </c>
       <c r="BM41" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 29.00 x 19.00 cm</t>
+          <t>31.00 x 11.00 x 21.00 cm</t>
         </is>
       </c>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>3.41 kg</t>
+          <t>2.71 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>3.41 kg</t>
+          <t>2.71 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>44.3 x 29.2 x 19.1 cm</t>
+          <t>46 x 23.1 x 16.5 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>44.30 x 29.20 x 19.10 cm</t>
+          <t>46.00 x 23.10 x 16.50 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17020,40 +16984,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B09RMQ1XLL</t>
+          <t>B0H2HYX6TQ</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX</t>
+          <t>VACTechPro</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2HYX6TQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX HSV3 Upright Vacuum CleanersLightweight 3-in-1 Compact Powerful Multifunction Corded Stick &amp; Handheld Vacuum | 600</t>
+          <t>VACTechPro Cordless Vacuum Cleaner, 35KPa/45Mins Lightweight Stick Vacuums6-in-1 Multi-Accessories, with Detachable Battery</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H2HYX6TQ?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71kT7Nk+6nL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B09RMQ1XLL</t>
+          <t>B0H2HYX6TQ</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -17067,13 +17031,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>6112</v>
+        <v>4825</v>
       </c>
       <c r="P42" s="15">
-        <v>2094</v>
+        <v>66783</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.26</v>
+        <v>0.93</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -17082,61 +17046,61 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>762</v>
+        <v>308</v>
       </c>
       <c r="U42" s="16">
-        <v>0.41</v>
+        <v>-0.09</v>
       </c>
       <c r="V42" s="15">
-        <v>25138</v>
+        <v>24637</v>
       </c>
       <c r="W42" s="15" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>300</t>
         </is>
       </c>
       <c r="X42" s="15">
-        <v>19194</v>
+        <v>27459</v>
       </c>
       <c r="Y42" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z42" s="20">
-        <v>32.99</v>
+        <v>79.99</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="15"/>
       <c r="AD42" s="19">
-        <v>4162</v>
+        <v>44</v>
       </c>
       <c r="AE42" s="15">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AF42" s="21">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.0105</v>
+        <v>0.11689999999999999</v>
       </c>
       <c r="AH42" s="20">
-        <v>4.87</v>
+        <v>3.71</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>1665</v>
+        <v>102</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
@@ -17150,11 +17114,11 @@
         <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Vytronix</t>
+          <t>HUIZHENG TECO</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
@@ -17164,25 +17128,21 @@
       </c>
       <c r="AU42" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV42" s="14" t="inlineStr">
         <is>
-          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+          <t>WAN CHAI 999077 HK</t>
         </is>
       </c>
       <c r="AW42" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN</t>
         </is>
       </c>
       <c r="AX42" s="13"/>
-      <c r="AY42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
@@ -17191,59 +17151,59 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD42" s="13"/>
+      <c r="BD42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE42" s="13"/>
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
-      <c r="BI42" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI42" s="23"/>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>2.4 kg</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>2.40 kg</t>
         </is>
       </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>31 x 11 x 21 cm</t>
+          <t>32.9 x 11.2 x 22 cm</t>
         </is>
       </c>
       <c r="BM42" s="23" t="inlineStr">
         <is>
-          <t>31.00 x 11.00 x 21.00 cm</t>
+          <t>32.90 x 11.20 x 22.00 cm</t>
         </is>
       </c>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>2.71 kg</t>
+          <t>3.52 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>2.71 kg</t>
+          <t>3.52 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>46 x 23.1 x 16.5 cm</t>
+          <t>43.9 x 27.2 x 19.5 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>46.00 x 23.10 x 16.50 cm</t>
+          <t>43.90 x 27.20 x 19.50 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17254,40 +17214,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0H2HYX6TQ</t>
+          <t>B0GQMGZBWP</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>VACTechPro</t>
+          <t>Tweakio</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2HYX6TQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Tweakio</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>VACTechPro Cordless Vacuum Cleaner, 35KPa/45Mins Lightweight Stick Vacuums6-in-1 Multi-Accessories, with Detachable Battery</t>
+          <t>Cordless Vacuum Cleaner, 550W/45KPA/60min Self-Standing Powerful Vacuum with LED Stylish Display,V-shaped Anti-Tangle Vacuum</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H2HYX6TQ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GQMGZBWP?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71kT7Nk+6nL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/612W687g-bL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0H2HYX6TQ</t>
+          <t>B0GQMGZBWP</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17301,13 +17261,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>4825</v>
+        <v>14700</v>
       </c>
       <c r="P43" s="15">
-        <v>66783</v>
+        <v>507</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.93</v>
+        <v>0.03</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17316,46 +17276,46 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="U43" s="16">
-        <v>-0.09</v>
+        <v>2.06</v>
       </c>
       <c r="V43" s="15">
-        <v>24637</v>
+        <v>24089</v>
       </c>
       <c r="W43" s="15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X43" s="15">
-        <v>27459</v>
+        <v>16932</v>
       </c>
       <c r="Y43" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>79.99</v>
+        <v>75.99</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="15"/>
       <c r="AD43" s="19">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AE43" s="15">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.11689999999999999</v>
+        <v>0.0536</v>
       </c>
       <c r="AH43" s="20">
         <v>3.71</v>
@@ -17366,11 +17326,11 @@
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
@@ -17388,7 +17348,7 @@
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>HUIZHENG TECO</t>
+          <t>Kuiyang Chaoxuan Small Store</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
@@ -17398,17 +17358,17 @@
       </c>
       <c r="AU43" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV43" s="14" t="inlineStr">
         <is>
-          <t>WAN CHAI 999077 HK</t>
+          <t>漯河市 河南 462000 CN</t>
         </is>
       </c>
       <c r="AW43" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A512ELTNL5ER</t>
         </is>
       </c>
       <c r="AX43" s="13"/>
@@ -17421,11 +17381,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD43" s="13"/>
       <c r="BE43" s="13"/>
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
@@ -17433,42 +17389,34 @@
       <c r="BI43" s="23"/>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>2.4 kg</t>
+          <t>3.5 kg</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>2.40 kg</t>
-        </is>
-      </c>
-      <c r="BL43" s="23" t="inlineStr">
-        <is>
-          <t>32.9 x 11.2 x 22 cm</t>
-        </is>
-      </c>
-      <c r="BM43" s="23" t="inlineStr">
-        <is>
-          <t>32.90 x 11.20 x 22.00 cm</t>
-        </is>
-      </c>
+          <t>3.50 kg</t>
+        </is>
+      </c>
+      <c r="BL43" s="23"/>
+      <c r="BM43" s="23"/>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>3.52 kg</t>
+          <t>4.2 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>3.52 kg</t>
+          <t>4.20 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>43.9 x 27.2 x 19.5 cm</t>
+          <t>41.1 x 32.2 x 20.2 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>43.90 x 27.20 x 19.50 cm</t>
+          <t>41.10 x 32.20 x 20.20 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
@@ -17484,40 +17432,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0GQMGZBWP</t>
+          <t>B0H8D9ZDGG</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Tweakio</t>
+          <t>Vexilar</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Tweakio</t>
+          <t>https://www.amazon.co.uk/stores/Home/page/DE49DE29-7A19-4585-91EF-0BF07D1037EE?lp_asin=B0H8D9ZDGG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Cordless Vacuum Cleaner, 550W/45KPA/60min Self-Standing Powerful Vacuum with LED Stylish Display,V-shaped Anti-Tangle Vacuum</t>
+          <t>Vexilar Vacuum Cleaner,550W/50Min Cordless Vacuum Cleaner,LED Touch Screens6-in-1 Lightweight Handheld Vacuum with Detachab</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GQMGZBWP?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H8D9ZDGG?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/612W687g-bL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/717Sx-GdShL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0GQMGZBWP</t>
+          <t>B0H8D9ZDGG</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17531,13 +17479,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>14700</v>
+        <v>24415</v>
       </c>
       <c r="P44" s="15">
-        <v>507</v>
+        <v>4391</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17546,46 +17494,46 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>61</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>317</v>
+        <v>228</v>
       </c>
       <c r="U44" s="16">
-        <v>2.06</v>
+        <v>88</v>
       </c>
       <c r="V44" s="15">
-        <v>24089</v>
+        <v>18238</v>
       </c>
       <c r="W44" s="15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X44" s="15">
-        <v>16932</v>
+        <v>9066</v>
       </c>
       <c r="Y44" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z44" s="20">
-        <v>75.99</v>
+        <v>79.99</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="15"/>
       <c r="AD44" s="19">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="AE44" s="15">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AF44" s="21">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.0536</v>
+        <v>0.0175</v>
       </c>
       <c r="AH44" s="20">
         <v>3.71</v>
@@ -17596,15 +17544,15 @@
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
@@ -17618,31 +17566,23 @@
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Kuiyang Chaoxuan Small Store</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU44" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV44" s="14" t="inlineStr">
-        <is>
-          <t>漯河市 河南 462000 CN</t>
-        </is>
-      </c>
-      <c r="AW44" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A512ELTNL5ER</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU44" s="13"/>
+      <c r="AV44" s="14"/>
+      <c r="AW44" s="13"/>
       <c r="AX44" s="13"/>
-      <c r="AY44" s="13"/>
+      <c r="AY44" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13"/>
@@ -17651,42 +17591,58 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD44" s="13"/>
+      <c r="BD44" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE44" s="13"/>
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
       <c r="BH44" s="14"/>
-      <c r="BI44" s="23"/>
+      <c r="BI44" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>3.5 kg</t>
+          <t>3.03 kg</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>3.50 kg</t>
-        </is>
-      </c>
-      <c r="BL44" s="23"/>
-      <c r="BM44" s="23"/>
+          <t>3.03 kg</t>
+        </is>
+      </c>
+      <c r="BL44" s="23" t="inlineStr">
+        <is>
+          <t>43.5 x 27.5 x 18 cm</t>
+        </is>
+      </c>
+      <c r="BM44" s="23" t="inlineStr">
+        <is>
+          <t>43.50 x 27.50 x 18.00 cm</t>
+        </is>
+      </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>4.2 kg</t>
+          <t>3.03 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>4.20 kg</t>
+          <t>3.03 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>41.1 x 32.2 x 20.2 cm</t>
+          <t>43.8 x 27.7 x 18.2 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>41.10 x 32.20 x 20.20 cm</t>
+          <t>43.80 x 27.70 x 18.20 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
@@ -17702,40 +17658,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0H8D9ZDGG</t>
+          <t>B0GYRSNRBH</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Vexilar</t>
+          <t>MONSGA</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Home/page/DE49DE29-7A19-4585-91EF-0BF07D1037EE?lp_asin=B0H8D9ZDGG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/MONSGA/page/187B188F-2741-4DDD-B2F5-BC3E82DB5363?lp_asin=B0GYRSNRBH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Vexilar Vacuum Cleaner,550W/50Min Cordless Vacuum Cleaner,LED Touch Screens6-in-1 Lightweight Handheld Vacuum with Detachab</t>
+          <t>MONSGA Cordless Vacuum Cleaner, 45KPa/550W/50Mins Lightweight Stick VacuumsLED Touch Screen, Detachable Battery, Anti-Tangl</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H8D9ZDGG?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GYRSNRBH?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/717Sx-GdShL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71XUczWOBCL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0H8D9ZDGG</t>
+          <t>B0GYRSNRBH</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17749,13 +17705,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>24415</v>
+        <v>11968</v>
       </c>
       <c r="P45" s="15">
-        <v>4391</v>
+        <v>6984</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.15</v>
+        <v>0.37</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17764,17 +17720,15 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>42</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>228</v>
-      </c>
-      <c r="U45" s="16">
-        <v>88</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="U45" s="16"/>
       <c r="V45" s="15">
-        <v>18238</v>
+        <v>16558</v>
       </c>
       <c r="W45" s="15" t="inlineStr">
         <is>
@@ -17782,43 +17736,43 @@
         </is>
       </c>
       <c r="X45" s="15">
-        <v>9066</v>
+        <v>10984</v>
       </c>
       <c r="Y45" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>79.99</v>
+        <v>89.99</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="15"/>
       <c r="AD45" s="19">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="AE45" s="15">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="AF45" s="21">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.0175</v>
+        <v>0.1848</v>
       </c>
       <c r="AH45" s="20">
         <v>3.71</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
@@ -17832,7 +17786,7 @@
         <v>10</v>
       </c>
       <c r="AR45" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
@@ -17848,11 +17802,7 @@
       <c r="AV45" s="14"/>
       <c r="AW45" s="13"/>
       <c r="AX45" s="13"/>
-      <c r="AY45" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
@@ -17861,58 +17811,50 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD45" s="13"/>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
-      <c r="BI45" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI45" s="23"/>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>3.03 kg</t>
+          <t>1.3 kg</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>3.03 kg</t>
+          <t>1.30 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>43.5 x 27.5 x 18 cm</t>
+          <t>31 x 20 x 12 cm</t>
         </is>
       </c>
       <c r="BM45" s="23" t="inlineStr">
         <is>
-          <t>43.50 x 27.50 x 18.00 cm</t>
+          <t>31.00 x 20.00 x 12.00 cm</t>
         </is>
       </c>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>3.03 kg</t>
+          <t>3.31 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>3.03 kg</t>
+          <t>3.31 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>43.8 x 27.7 x 18.2 cm</t>
+          <t>43.8 x 28.1 x 19.7 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>43.80 x 27.70 x 18.20 cm</t>
+          <t>43.80 x 28.10 x 19.70 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
@@ -17928,40 +17870,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0GYRSNRBH</t>
+          <t>B0H3N8MK58</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>MONSGA</t>
+          <t>VACLANY</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/MONSGA/page/187B188F-2741-4DDD-B2F5-BC3E82DB5363?lp_asin=B0GYRSNRBH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0H3N8MK58&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>MONSGA Cordless Vacuum Cleaner, 45KPa/550W/50Mins Lightweight Stick VacuumsLED Touch Screen, Detachable Battery, Anti-Tangl</t>
+          <t>L12E Cordless Vacuum Cleaner, 46KPa/400W Powerful Stick Vacuum, 1L DustbinsHandheld Cordless Vacuum, Removable Battery, Wal</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GYRSNRBH?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H3N8MK58?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71XUczWOBCL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61Y41LdD4xL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0GYRSNRBH</t>
+          <t>B0H3N8MK58</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17975,13 +17917,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>11968</v>
+        <v>8549</v>
       </c>
       <c r="P46" s="15">
-        <v>6984</v>
+        <v>2929</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -17990,87 +17932,101 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>184</v>
-      </c>
-      <c r="U46" s="16"/>
+        <v>265</v>
+      </c>
+      <c r="U46" s="16">
+        <v>1.04</v>
+      </c>
       <c r="V46" s="15">
-        <v>16558</v>
+        <v>15897</v>
       </c>
       <c r="W46" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X46" s="15">
-        <v>10984</v>
+        <v>13664</v>
       </c>
       <c r="Y46" s="19">
         <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>89.99</v>
+        <v>59.99</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="15"/>
       <c r="AD46" s="19">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="AE46" s="15">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.1848</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="20">
         <v>3.71</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
       <c r="AQ46" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR46" s="19">
         <v>1</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>VAC LAN LTD.</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>PULBOROUGH RH20 3BX GB</t>
+        </is>
+      </c>
+      <c r="AW46" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN</t>
+        </is>
+      </c>
       <c r="AX46" s="13"/>
       <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
@@ -18089,42 +18045,42 @@
       <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>1.3 kg</t>
+          <t>3.46 kg</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>1.30 kg</t>
+          <t>3.46 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>31 x 20 x 12 cm</t>
+          <t>23 x 25 x 117 cm</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>31.00 x 20.00 x 12.00 cm</t>
+          <t>23.00 x 25.00 x 117.00 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>3.31 kg</t>
+          <t>3.46 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>3.31 kg</t>
+          <t>3.46 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>43.8 x 28.1 x 19.7 cm</t>
+          <t>44.1 x 28.1 x 18.6 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>43.80 x 28.10 x 19.70 cm</t>
+          <t>44.10 x 28.10 x 18.60 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
@@ -18140,40 +18096,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0H3N8MK58</t>
+          <t>B0G1YQ9T93</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>VACLANY</t>
+          <t>Levoit</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0H3N8MK58&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0G1YQ9T93&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>L12E Cordless Vacuum Cleaner, 46KPa/400W Powerful Stick Vacuum, 1L DustbinsHandheld Cordless Vacuum, Removable Battery, Wal</t>
+          <t>Levoit Cordless Vacuum Cleaner, Anti-Hair Wrap, 100,000 RPM Brushless Motors99.7% Hard Floor Clean, Up to 50 Min Runtime, 5</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H3N8MK58?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0G1YQ9T93?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61Y41LdD4xL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61GsdjWeYnL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0H3N8MK58</t>
+          <t>B0G1YQ9T93</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -18187,13 +18143,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>8549</v>
+        <v>25018</v>
       </c>
       <c r="P47" s="15">
-        <v>2929</v>
+        <v>7619</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -18202,43 +18158,43 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>63</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="U47" s="16">
-        <v>1.04</v>
+        <v>-0.12</v>
       </c>
       <c r="V47" s="15">
-        <v>15897</v>
+        <v>12757</v>
       </c>
       <c r="W47" s="15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X47" s="15">
-        <v>13664</v>
+        <v>5914</v>
       </c>
       <c r="Y47" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z47" s="20">
-        <v>59.99</v>
+        <v>109.97</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="15"/>
       <c r="AD47" s="19">
-        <v>8</v>
+        <v>4880</v>
       </c>
       <c r="AE47" s="15">
         <v>0</v>
       </c>
       <c r="AF47" s="21">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
@@ -18247,58 +18203,50 @@
         <v>3.71</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>34</v>
+        <v>292</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
       <c r="AQ47" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR47" s="19">
         <v>1</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>VAC LAN LTD.</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU47" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV47" s="14" t="inlineStr">
-        <is>
-          <t>PULBOROUGH RH20 3BX GB</t>
-        </is>
-      </c>
-      <c r="AW47" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU47" s="13"/>
+      <c r="AV47" s="14"/>
+      <c r="AW47" s="13"/>
       <c r="AX47" s="13"/>
-      <c r="AY47" s="13"/>
+      <c r="AY47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
@@ -18307,50 +18255,58 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD47" s="13"/>
+      <c r="BD47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE47" s="13"/>
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
-      <c r="BI47" s="23"/>
+      <c r="BI47" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>3.46 kg</t>
+          <t>2.79 kg</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>3.46 kg</t>
+          <t>2.79 kg</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>23 x 25 x 117 cm</t>
+          <t>110 x 19.5 x 25 cm</t>
         </is>
       </c>
       <c r="BM47" s="23" t="inlineStr">
         <is>
-          <t>23.00 x 25.00 x 117.00 cm</t>
+          <t>110.00 x 19.50 x 25.00 cm</t>
         </is>
       </c>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>3.46 kg</t>
+          <t>4.67 kg</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>3.46 kg</t>
+          <t>4.67 kg</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>44.1 x 28.1 x 18.6 cm</t>
+          <t>44.9 x 33.6 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>44.10 x 28.10 x 18.60 cm</t>
+          <t>44.90 x 33.60 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
@@ -18366,40 +18322,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0G1YQ9T93</t>
+          <t>B0FGPM83WQ</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Levoit</t>
+          <t>Vlihapy</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0G1YQ9T93&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Levoit Cordless Vacuum Cleaner, Anti-Hair Wrap, 100,000 RPM Brushless Motors99.7% Hard Floor Clean, Up to 50 Min Runtime, 5</t>
+          <t>6 IN 1 Cordless Vacuum Cleaner 160W 15000PA Powerful Stick Vacuums &amp; Electric Brooms with LED, 3000mAh Rechargeable Battery,</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0G1YQ9T93?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61GsdjWeYnL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0G1YQ9T93</t>
+          <t>B0FGPM83WQ</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18413,13 +18369,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>25018</v>
+        <v>10553</v>
       </c>
       <c r="P48" s="15">
-        <v>7619</v>
+        <v>30828</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.23</v>
+        <v>0.75</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18428,89 +18384,99 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>116</v>
+        <v>248</v>
       </c>
       <c r="U48" s="16">
-        <v>-0.12</v>
+        <v>0.47</v>
       </c>
       <c r="V48" s="15">
-        <v>12757</v>
+        <v>7931</v>
       </c>
       <c r="W48" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X48" s="15">
-        <v>5914</v>
+        <v>8594</v>
       </c>
       <c r="Y48" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z48" s="20">
-        <v>109.97</v>
+        <v>42.97</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="15"/>
       <c r="AD48" s="19">
-        <v>4880</v>
+        <v>20</v>
       </c>
       <c r="AE48" s="15">
+        <v>9</v>
+      </c>
+      <c r="AF48" s="21">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="22">
+        <v>0.0363</v>
+      </c>
+      <c r="AH48" s="20"/>
+      <c r="AI48" s="16">
         <v>0</v>
-      </c>
-      <c r="AF48" s="21">
-        <v>4.7</v>
-      </c>
-      <c r="AG48" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="20">
-        <v>3.71</v>
-      </c>
-      <c r="AI48" s="16">
-        <v>0.97</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>292</v>
+        <v>424</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
       <c r="AQ48" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR48" s="19">
         <v>1</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Treasuretool</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU48" s="13"/>
-      <c r="AV48" s="14"/>
-      <c r="AW48" s="13"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU48" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV48" s="14" t="inlineStr">
+        <is>
+          <t>南通市 崇川区 江苏省 226014 CN</t>
+        </is>
+      </c>
+      <c r="AW48" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827</t>
+        </is>
+      </c>
       <c r="AX48" s="13"/>
       <c r="AY48" s="13" t="inlineStr">
         <is>
@@ -18520,11 +18486,7 @@
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
-      <c r="BC48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC48" s="13"/>
       <c r="BD48" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18539,51 +18501,23 @@
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ48" s="23" t="inlineStr">
-        <is>
-          <t>2.79 kg</t>
-        </is>
-      </c>
-      <c r="BK48" s="23" t="inlineStr">
-        <is>
-          <t>2.79 kg</t>
-        </is>
-      </c>
+      <c r="BJ48" s="23"/>
+      <c r="BK48" s="23"/>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>110 x 19.5 x 25 cm</t>
+          <t>23.5 x 15 x 110 cm</t>
         </is>
       </c>
       <c r="BM48" s="23" t="inlineStr">
         <is>
-          <t>110.00 x 19.50 x 25.00 cm</t>
-        </is>
-      </c>
-      <c r="BN48" s="23" t="inlineStr">
-        <is>
-          <t>4.67 kg</t>
-        </is>
-      </c>
-      <c r="BO48" s="23" t="inlineStr">
-        <is>
-          <t>4.67 kg</t>
-        </is>
-      </c>
-      <c r="BP48" s="23" t="inlineStr">
-        <is>
-          <t>44.9 x 33.6 x 19.4 cm</t>
-        </is>
-      </c>
-      <c r="BQ48" s="23" t="inlineStr">
-        <is>
-          <t>44.90 x 33.60 x 19.40 cm</t>
-        </is>
-      </c>
-      <c r="BR48" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+          <t>23.50 x 15.00 x 110.00 cm</t>
+        </is>
+      </c>
+      <c r="BN48" s="23"/>
+      <c r="BO48" s="23"/>
+      <c r="BP48" s="23"/>
+      <c r="BQ48" s="23"/>
+      <c r="BR48" s="13"/>
     </row>
     <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13">
@@ -18592,40 +18526,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0FGPM83WQ</t>
+          <t>B0HCZSDT7B</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>Vlihapy</t>
+          <t>Powerffy</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy</t>
+          <t>https://www.amazon.co.uk/stores/Powerffy/page/453D7331-480E-4E68-8A51-345F97F1A598?lp_asin=B0HCZSDT7B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>6 IN 1 Cordless Vacuum Cleaner 160W 15000PA Powerful Stick Vacuums &amp; Electric Brooms with LED, 3000mAh Rechargeable Battery,</t>
+          <t>Powerffy Cordless Vacuum Cleaner, 45KPa 600W Powerful Stick Vacuum for Home, 60Mins Runtime, 1.8L XL Dust Cup One-Touch Empty</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HCZSDT7B?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Aq5wnxS3L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0FGPM83WQ</t>
+          <t>B0HCZSDT7B</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -18639,10 +18573,10 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>10553</v>
+        <v>32860</v>
       </c>
       <c r="P49" s="15">
-        <v>30828</v>
+        <v>96240</v>
       </c>
       <c r="Q49" s="16">
         <v>0.75</v>
@@ -18654,82 +18588,82 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>248</v>
-      </c>
-      <c r="U49" s="16">
-        <v>0.47</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="U49" s="16"/>
       <c r="V49" s="15">
-        <v>7931</v>
+        <v>5999</v>
       </c>
       <c r="W49" s="15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X49" s="15">
-        <v>8594</v>
+        <v>5673</v>
       </c>
       <c r="Y49" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="20">
-        <v>42.97</v>
+        <v>99.99</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE49" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF49" s="21">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.0363</v>
-      </c>
-      <c r="AH49" s="20"/>
+        <v>0.1167</v>
+      </c>
+      <c r="AH49" s="20">
+        <v>3.71</v>
+      </c>
       <c r="AI49" s="16">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>424</v>
+        <v>28</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49"/>
       <c r="AQ49" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR49" s="19">
         <v>1</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>Treasuretool</t>
+          <t>ELUCK</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU49" s="13" t="inlineStr">
@@ -18739,12 +18673,12 @@
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>南通市 崇川区 江苏省 226014 CN</t>
+          <t>longgangqu guangdong 518000 CN</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A75TZJLR7NPZB</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
@@ -18756,7 +18690,11 @@
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
-      <c r="BC49" s="13"/>
+      <c r="BC49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD49" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18771,23 +18709,51 @@
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ49" s="23"/>
-      <c r="BK49" s="23"/>
+      <c r="BJ49" s="23" t="inlineStr">
+        <is>
+          <t>2.88 kg</t>
+        </is>
+      </c>
+      <c r="BK49" s="23" t="inlineStr">
+        <is>
+          <t>2.88 kg</t>
+        </is>
+      </c>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>23.5 x 15 x 110 cm</t>
+          <t>40 x 33 x 19 cm</t>
         </is>
       </c>
       <c r="BM49" s="23" t="inlineStr">
         <is>
-          <t>23.50 x 15.00 x 110.00 cm</t>
-        </is>
-      </c>
-      <c r="BN49" s="23"/>
-      <c r="BO49" s="23"/>
-      <c r="BP49" s="23"/>
-      <c r="BQ49" s="23"/>
-      <c r="BR49" s="13"/>
+          <t>40.00 x 33.00 x 19.00 cm</t>
+        </is>
+      </c>
+      <c r="BN49" s="23" t="inlineStr">
+        <is>
+          <t>3.88 kg</t>
+        </is>
+      </c>
+      <c r="BO49" s="23" t="inlineStr">
+        <is>
+          <t>3.88 kg</t>
+        </is>
+      </c>
+      <c r="BP49" s="23" t="inlineStr">
+        <is>
+          <t>44 x 33.2 x 19.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ49" s="23" t="inlineStr">
+        <is>
+          <t>44.00 x 33.20 x 19.20 cm</t>
+        </is>
+      </c>
+      <c r="BR49" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
@@ -18796,40 +18762,40 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0HCZSDT7B</t>
+          <t>B0GQ66CNX6</t>
         </is>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Powerffy</t>
+          <t>Vexilar</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Powerffy/page/453D7331-480E-4E68-8A51-345F97F1A598?lp_asin=B0HCZSDT7B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/Home/page/DE49DE29-7A19-4585-91EF-0BF07D1037EE?lp_asin=B0GQ66CNX6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Powerffy Cordless Vacuum Cleaner, 45KPa 600W Powerful Stick Vacuum for Home, 60Mins Runtime, 1.8L XL Dust Cup One-Touch Empty</t>
+          <t>Vexilar V10Pro Cordless Vacuum Cleaner, 550W 45Kpa Stick Vacuum with Touch Display, Up to 45Mins Runtime, Detachable Battery,</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0HCZSDT7B?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GQ66CNX6?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Aq5wnxS3L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71IdvHswVqL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0HCZSDT7B</t>
+          <t>B0GQ66CNX6</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -18843,13 +18809,13 @@
         </is>
       </c>
       <c r="O50" s="15">
-        <v>32860</v>
+        <v>9915</v>
       </c>
       <c r="P50" s="15">
-        <v>96240</v>
+        <v>494458</v>
       </c>
       <c r="Q50" s="16">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="R50" s="17" t="inlineStr">
         <is>
@@ -18858,15 +18824,17 @@
       </c>
       <c r="S50" s="18" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T50" s="15">
-        <v>60</v>
-      </c>
-      <c r="U50" s="16"/>
+        <v>54</v>
+      </c>
+      <c r="U50" s="16">
+        <v>-0.95</v>
+      </c>
       <c r="V50" s="15">
-        <v>5999</v>
+        <v>3671</v>
       </c>
       <c r="W50" s="15" t="inlineStr">
         <is>
@@ -18874,47 +18842,47 @@
         </is>
       </c>
       <c r="X50" s="15">
-        <v>5673</v>
+        <v>4305</v>
       </c>
       <c r="Y50" s="19">
         <v>1</v>
       </c>
       <c r="Z50" s="20">
-        <v>99.99</v>
+        <v>67.99</v>
       </c>
       <c r="AA50"/>
       <c r="AB50"/>
       <c r="AC50" s="15"/>
       <c r="AD50" s="19">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="AE50" s="15">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AF50" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG50" s="22">
-        <v>0.1167</v>
+        <v>0.2593</v>
       </c>
       <c r="AH50" s="20">
         <v>3.71</v>
       </c>
       <c r="AI50" s="16">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AJ50"/>
       <c r="AK50" s="13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AL50" s="19">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="AM50" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN50" s="13"/>
@@ -18928,29 +18896,17 @@
       </c>
       <c r="AS50" s="14" t="inlineStr">
         <is>
-          <t>ELUCK</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT50" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>longgangqu guangdong 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A75TZJLR7NPZB</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU50" s="13"/>
+      <c r="AV50" s="14"/>
+      <c r="AW50" s="13"/>
       <c r="AX50" s="13"/>
       <c r="AY50" s="13" t="inlineStr">
         <is>
@@ -18981,271 +18937,45 @@
       </c>
       <c r="BJ50" s="23" t="inlineStr">
         <is>
-          <t>2.88 kg</t>
+          <t>2.8 kg</t>
         </is>
       </c>
       <c r="BK50" s="23" t="inlineStr">
         <is>
-          <t>2.88 kg</t>
+          <t>2.80 kg</t>
         </is>
       </c>
       <c r="BL50" s="23" t="inlineStr">
         <is>
-          <t>40 x 33 x 19 cm</t>
+          <t>25 x 23 x 12.4 cm</t>
         </is>
       </c>
       <c r="BM50" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 33.00 x 19.00 cm</t>
+          <t>25.00 x 23.00 x 12.40 cm</t>
         </is>
       </c>
       <c r="BN50" s="23" t="inlineStr">
         <is>
-          <t>3.88 kg</t>
+          <t>3.03 kg</t>
         </is>
       </c>
       <c r="BO50" s="23" t="inlineStr">
         <is>
-          <t>3.88 kg</t>
+          <t>3.03 kg</t>
         </is>
       </c>
       <c r="BP50" s="23" t="inlineStr">
         <is>
-          <t>44 x 33.2 x 19.2 cm</t>
+          <t>43.6 x 27.5 x 18.1 cm</t>
         </is>
       </c>
       <c r="BQ50" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 33.20 x 19.20 cm</t>
+          <t>43.60 x 27.50 x 18.10 cm</t>
         </is>
       </c>
       <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0GQ66CNX6</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Vexilar</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/Home/page/DE49DE29-7A19-4585-91EF-0BF07D1037EE?lp_asin=B0GQ66CNX6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Vexilar V10Pro Cordless Vacuum Cleaner, 550W 45Kpa Stick Vacuum with Touch Display, Up to 45Mins Runtime, Detachable Battery,</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0GQ66CNX6?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71IdvHswVqL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0GQ66CNX6</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>9915</v>
-      </c>
-      <c r="P51" s="15">
-        <v>494458</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.98</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>54</v>
-      </c>
-      <c r="U51" s="16">
-        <v>-0.95</v>
-      </c>
-      <c r="V51" s="15">
-        <v>3671</v>
-      </c>
-      <c r="W51" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X51" s="15">
-        <v>4305</v>
-      </c>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>67.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>133</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>14</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.2</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0.2593</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>3.71</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.95</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>188</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>2.8 kg</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>2.80 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>25 x 23 x 12.4 cm</t>
-        </is>
-      </c>
-      <c r="BM51" s="23" t="inlineStr">
-        <is>
-          <t>25.00 x 23.00 x 12.40 cm</t>
-        </is>
-      </c>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>3.03 kg</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>3.03 kg</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>43.6 x 27.5 x 18.1 cm</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>43.60 x 27.50 x 18.10 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
@@ -19516,120 +19246,113 @@
     <hyperlink ref="M36" r:id="rId259" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N36" r:id="rId260"/>
     <hyperlink ref="AW36" r:id="rId261" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3MDIOSFOSE57L"/>
-    <hyperlink ref="C37" r:id="rId262" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
-    <hyperlink ref="G37" r:id="rId263" tooltip="https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0F9YPP9C3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J37" r:id="rId264" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1"/>
-    <hyperlink ref="K37" r:id="rId265" tooltip="https://images-na.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId266" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
+    <hyperlink ref="C37" r:id="rId262" tooltip="https://www.amazon.co.uk/dp/B0DJ71KLJG"/>
+    <hyperlink ref="G37" r:id="rId263" tooltip="https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0DJ71KLJG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId264" tooltip="https://www.amazon.co.uk/dp/B0DJ71KLJG?psc=1"/>
+    <hyperlink ref="K37" r:id="rId265" tooltip="https://m.media-amazon.com/images/I/41a3F1M66OL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId266" tooltip="https://www.amazon.co.uk/dp/B0DJ71KLJG"/>
     <hyperlink ref="M37" r:id="rId267" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N37" r:id="rId268"/>
-    <hyperlink ref="C38" r:id="rId269" tooltip="https://www.amazon.co.uk/dp/B0DJ71KLJG"/>
-    <hyperlink ref="G38" r:id="rId270" tooltip="https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0DJ71KLJG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId271" tooltip="https://www.amazon.co.uk/dp/B0DJ71KLJG?psc=1"/>
-    <hyperlink ref="K38" r:id="rId272" tooltip="https://m.media-amazon.com/images/I/41a3F1M66OL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId273" tooltip="https://www.amazon.co.uk/dp/B0DJ71KLJG"/>
+    <hyperlink ref="C38" r:id="rId269" tooltip="https://www.amazon.co.uk/dp/B09SG94978"/>
+    <hyperlink ref="G38" r:id="rId270" tooltip="https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09SG94978&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId271" tooltip="https://www.amazon.co.uk/dp/B09SG94978?psc=1"/>
+    <hyperlink ref="K38" r:id="rId272" tooltip="https://images-na.ssl-images-amazon.com/images/I/51U8DhXUrWL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId273" tooltip="https://www.amazon.co.uk/dp/B09SG94978"/>
     <hyperlink ref="M38" r:id="rId274" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N38" r:id="rId275"/>
-    <hyperlink ref="C39" r:id="rId276" tooltip="https://www.amazon.co.uk/dp/B09SG94978"/>
-    <hyperlink ref="G39" r:id="rId277" tooltip="https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09SG94978&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId278" tooltip="https://www.amazon.co.uk/dp/B09SG94978?psc=1"/>
-    <hyperlink ref="K39" r:id="rId279" tooltip="https://images-na.ssl-images-amazon.com/images/I/51U8DhXUrWL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId280" tooltip="https://www.amazon.co.uk/dp/B09SG94978"/>
+    <hyperlink ref="C39" r:id="rId276" tooltip="https://www.amazon.co.uk/dp/B0746H6J2R"/>
+    <hyperlink ref="G39" r:id="rId277" tooltip="https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0746H6J2R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId278" tooltip="https://www.amazon.co.uk/dp/B0746H6J2R?psc=1"/>
+    <hyperlink ref="K39" r:id="rId279" tooltip="https://images-na.ssl-images-amazon.com/images/I/71O74t-35IL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId280" tooltip="https://www.amazon.co.uk/dp/B0746H6J2R"/>
     <hyperlink ref="M39" r:id="rId281" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N39" r:id="rId282"/>
-    <hyperlink ref="C40" r:id="rId283" tooltip="https://www.amazon.co.uk/dp/B0746H6J2R"/>
-    <hyperlink ref="G40" r:id="rId284" tooltip="https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0746H6J2R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId285" tooltip="https://www.amazon.co.uk/dp/B0746H6J2R?psc=1"/>
-    <hyperlink ref="K40" r:id="rId286" tooltip="https://images-na.ssl-images-amazon.com/images/I/71O74t-35IL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B0746H6J2R"/>
-    <hyperlink ref="M40" r:id="rId288" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N40" r:id="rId289"/>
-    <hyperlink ref="AW40" r:id="rId290" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6"/>
-    <hyperlink ref="C41" r:id="rId291" tooltip="https://www.amazon.co.uk/dp/B0GHKWY3KT"/>
-    <hyperlink ref="G41" r:id="rId292" tooltip="https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0GHKWY3KT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId293" tooltip="https://www.amazon.co.uk/dp/B0GHKWY3KT?psc=1"/>
-    <hyperlink ref="K41" r:id="rId294" tooltip="https://images-na.ssl-images-amazon.com/images/I/71t+DWqwinL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId295" tooltip="https://www.amazon.co.uk/dp/B0GHKWY3KT"/>
+    <hyperlink ref="AW39" r:id="rId283" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6"/>
+    <hyperlink ref="C40" r:id="rId284" tooltip="https://www.amazon.co.uk/dp/B0GHKWY3KT"/>
+    <hyperlink ref="G40" r:id="rId285" tooltip="https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0GHKWY3KT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J40" r:id="rId286" tooltip="https://www.amazon.co.uk/dp/B0GHKWY3KT?psc=1"/>
+    <hyperlink ref="K40" r:id="rId287" tooltip="https://images-na.ssl-images-amazon.com/images/I/71t+DWqwinL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId288" tooltip="https://www.amazon.co.uk/dp/B0GHKWY3KT"/>
+    <hyperlink ref="M40" r:id="rId289" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N40" r:id="rId290"/>
+    <hyperlink ref="C41" r:id="rId291" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
+    <hyperlink ref="G41" r:id="rId292" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J41" r:id="rId293" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1"/>
+    <hyperlink ref="K41" r:id="rId294" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId295" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
     <hyperlink ref="M41" r:id="rId296" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N41" r:id="rId297"/>
-    <hyperlink ref="C42" r:id="rId298" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
-    <hyperlink ref="G42" r:id="rId299" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J42" r:id="rId300" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1"/>
-    <hyperlink ref="K42" r:id="rId301" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId302" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
-    <hyperlink ref="M42" r:id="rId303" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N42" r:id="rId304"/>
-    <hyperlink ref="AW42" r:id="rId305" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
-    <hyperlink ref="C43" r:id="rId306" tooltip="https://www.amazon.co.uk/dp/B0H2HYX6TQ"/>
-    <hyperlink ref="G43" r:id="rId307" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2HYX6TQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J43" r:id="rId308" tooltip="https://www.amazon.co.uk/dp/B0H2HYX6TQ?psc=1"/>
-    <hyperlink ref="K43" r:id="rId309" tooltip="https://images-na.ssl-images-amazon.com/images/I/71kT7Nk+6nL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B0H2HYX6TQ"/>
-    <hyperlink ref="M43" r:id="rId311" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N43" r:id="rId312"/>
-    <hyperlink ref="AW43" r:id="rId313" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN"/>
-    <hyperlink ref="C44" r:id="rId314" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP"/>
-    <hyperlink ref="G44" r:id="rId315" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Tweakio"/>
-    <hyperlink ref="J44" r:id="rId316" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP?psc=1"/>
-    <hyperlink ref="K44" r:id="rId317" tooltip="https://images-na.ssl-images-amazon.com/images/I/612W687g-bL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId318" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP"/>
-    <hyperlink ref="M44" r:id="rId319" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N44" r:id="rId320"/>
-    <hyperlink ref="AW44" r:id="rId321" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A512ELTNL5ER"/>
-    <hyperlink ref="C45" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B0H8D9ZDGG"/>
-    <hyperlink ref="G45" r:id="rId323" tooltip="https://www.amazon.co.uk/stores/Home/page/DE49DE29-7A19-4585-91EF-0BF07D1037EE?lp_asin=B0H8D9ZDGG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId324" tooltip="https://www.amazon.co.uk/dp/B0H8D9ZDGG?psc=1"/>
-    <hyperlink ref="K45" r:id="rId325" tooltip="https://images-na.ssl-images-amazon.com/images/I/717Sx-GdShL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId326" tooltip="https://www.amazon.co.uk/dp/B0H8D9ZDGG"/>
+    <hyperlink ref="AW41" r:id="rId298" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
+    <hyperlink ref="C42" r:id="rId299" tooltip="https://www.amazon.co.uk/dp/B0H2HYX6TQ"/>
+    <hyperlink ref="G42" r:id="rId300" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2HYX6TQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J42" r:id="rId301" tooltip="https://www.amazon.co.uk/dp/B0H2HYX6TQ?psc=1"/>
+    <hyperlink ref="K42" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/71kT7Nk+6nL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId303" tooltip="https://www.amazon.co.uk/dp/B0H2HYX6TQ"/>
+    <hyperlink ref="M42" r:id="rId304" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N42" r:id="rId305"/>
+    <hyperlink ref="AW42" r:id="rId306" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN"/>
+    <hyperlink ref="C43" r:id="rId307" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP"/>
+    <hyperlink ref="G43" r:id="rId308" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Tweakio"/>
+    <hyperlink ref="J43" r:id="rId309" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP?psc=1"/>
+    <hyperlink ref="K43" r:id="rId310" tooltip="https://images-na.ssl-images-amazon.com/images/I/612W687g-bL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId311" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP"/>
+    <hyperlink ref="M43" r:id="rId312" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N43" r:id="rId313"/>
+    <hyperlink ref="AW43" r:id="rId314" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1A512ELTNL5ER"/>
+    <hyperlink ref="C44" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B0H8D9ZDGG"/>
+    <hyperlink ref="G44" r:id="rId316" tooltip="https://www.amazon.co.uk/stores/Home/page/DE49DE29-7A19-4585-91EF-0BF07D1037EE?lp_asin=B0H8D9ZDGG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B0H8D9ZDGG?psc=1"/>
+    <hyperlink ref="K44" r:id="rId318" tooltip="https://images-na.ssl-images-amazon.com/images/I/717Sx-GdShL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId319" tooltip="https://www.amazon.co.uk/dp/B0H8D9ZDGG"/>
+    <hyperlink ref="M44" r:id="rId320" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N44" r:id="rId321"/>
+    <hyperlink ref="C45" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B0GYRSNRBH"/>
+    <hyperlink ref="G45" r:id="rId323" tooltip="https://www.amazon.co.uk/stores/MONSGA/page/187B188F-2741-4DDD-B2F5-BC3E82DB5363?lp_asin=B0GYRSNRBH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId324" tooltip="https://www.amazon.co.uk/dp/B0GYRSNRBH?psc=1"/>
+    <hyperlink ref="K45" r:id="rId325" tooltip="https://images-na.ssl-images-amazon.com/images/I/71XUczWOBCL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId326" tooltip="https://www.amazon.co.uk/dp/B0GYRSNRBH"/>
     <hyperlink ref="M45" r:id="rId327" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N45" r:id="rId328"/>
-    <hyperlink ref="C46" r:id="rId329" tooltip="https://www.amazon.co.uk/dp/B0GYRSNRBH"/>
-    <hyperlink ref="G46" r:id="rId330" tooltip="https://www.amazon.co.uk/stores/MONSGA/page/187B188F-2741-4DDD-B2F5-BC3E82DB5363?lp_asin=B0GYRSNRBH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId331" tooltip="https://www.amazon.co.uk/dp/B0GYRSNRBH?psc=1"/>
-    <hyperlink ref="K46" r:id="rId332" tooltip="https://images-na.ssl-images-amazon.com/images/I/71XUczWOBCL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId333" tooltip="https://www.amazon.co.uk/dp/B0GYRSNRBH"/>
+    <hyperlink ref="C46" r:id="rId329" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58"/>
+    <hyperlink ref="G46" r:id="rId330" tooltip="https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0H3N8MK58&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J46" r:id="rId331" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58?psc=1"/>
+    <hyperlink ref="K46" r:id="rId332" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Y41LdD4xL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId333" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58"/>
     <hyperlink ref="M46" r:id="rId334" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N46" r:id="rId335"/>
-    <hyperlink ref="C47" r:id="rId336" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58"/>
-    <hyperlink ref="G47" r:id="rId337" tooltip="https://www.amazon.co.uk/stores/VACLANY/page/27A8BC2B-2808-4919-A21E-51D1F809493C?lp_asin=B0H3N8MK58&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J47" r:id="rId338" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58?psc=1"/>
-    <hyperlink ref="K47" r:id="rId339" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Y41LdD4xL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId340" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58"/>
-    <hyperlink ref="M47" r:id="rId341" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N47" r:id="rId342"/>
-    <hyperlink ref="AW47" r:id="rId343" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN"/>
-    <hyperlink ref="C48" r:id="rId344" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93"/>
-    <hyperlink ref="G48" r:id="rId345" tooltip="https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0G1YQ9T93&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId346" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93?psc=1"/>
-    <hyperlink ref="K48" r:id="rId347" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GsdjWeYnL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId348" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93"/>
+    <hyperlink ref="AW46" r:id="rId336" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2THPY6GBHGESN"/>
+    <hyperlink ref="C47" r:id="rId337" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93"/>
+    <hyperlink ref="G47" r:id="rId338" tooltip="https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0G1YQ9T93&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId339" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93?psc=1"/>
+    <hyperlink ref="K47" r:id="rId340" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GsdjWeYnL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId341" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93"/>
+    <hyperlink ref="M47" r:id="rId342" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N47" r:id="rId343"/>
+    <hyperlink ref="C48" r:id="rId344" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
+    <hyperlink ref="G48" r:id="rId345" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy"/>
+    <hyperlink ref="J48" r:id="rId346" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1"/>
+    <hyperlink ref="K48" r:id="rId347" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId348" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
     <hyperlink ref="M48" r:id="rId349" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N48" r:id="rId350"/>
-    <hyperlink ref="C49" r:id="rId351" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
-    <hyperlink ref="G49" r:id="rId352" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy"/>
-    <hyperlink ref="J49" r:id="rId353" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1"/>
-    <hyperlink ref="K49" r:id="rId354" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId355" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
-    <hyperlink ref="M49" r:id="rId356" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N49" r:id="rId357"/>
-    <hyperlink ref="AW49" r:id="rId358" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827"/>
-    <hyperlink ref="C50" r:id="rId359" tooltip="https://www.amazon.co.uk/dp/B0HCZSDT7B"/>
-    <hyperlink ref="G50" r:id="rId360" tooltip="https://www.amazon.co.uk/stores/Powerffy/page/453D7331-480E-4E68-8A51-345F97F1A598?lp_asin=B0HCZSDT7B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId361" tooltip="https://www.amazon.co.uk/dp/B0HCZSDT7B?psc=1"/>
-    <hyperlink ref="K50" r:id="rId362" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Aq5wnxS3L._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId363" tooltip="https://www.amazon.co.uk/dp/B0HCZSDT7B"/>
-    <hyperlink ref="M50" r:id="rId364" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N50" r:id="rId365"/>
-    <hyperlink ref="AW50" r:id="rId366" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A75TZJLR7NPZB"/>
-    <hyperlink ref="C51" r:id="rId367" tooltip="https://www.amazon.co.uk/dp/B0GQ66CNX6"/>
-    <hyperlink ref="G51" r:id="rId368" tooltip="https://www.amazon.co.uk/stores/Home/page/DE49DE29-7A19-4585-91EF-0BF07D1037EE?lp_asin=B0GQ66CNX6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J51" r:id="rId369" tooltip="https://www.amazon.co.uk/dp/B0GQ66CNX6?psc=1"/>
-    <hyperlink ref="K51" r:id="rId370" tooltip="https://images-na.ssl-images-amazon.com/images/I/71IdvHswVqL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId371" tooltip="https://www.amazon.co.uk/dp/B0GQ66CNX6"/>
-    <hyperlink ref="M51" r:id="rId372" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N51" r:id="rId373"/>
+    <hyperlink ref="AW48" r:id="rId351" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827"/>
+    <hyperlink ref="C49" r:id="rId352" tooltip="https://www.amazon.co.uk/dp/B0HCZSDT7B"/>
+    <hyperlink ref="G49" r:id="rId353" tooltip="https://www.amazon.co.uk/stores/Powerffy/page/453D7331-480E-4E68-8A51-345F97F1A598?lp_asin=B0HCZSDT7B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J49" r:id="rId354" tooltip="https://www.amazon.co.uk/dp/B0HCZSDT7B?psc=1"/>
+    <hyperlink ref="K49" r:id="rId355" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Aq5wnxS3L._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId356" tooltip="https://www.amazon.co.uk/dp/B0HCZSDT7B"/>
+    <hyperlink ref="M49" r:id="rId357" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N49" r:id="rId358"/>
+    <hyperlink ref="AW49" r:id="rId359" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A75TZJLR7NPZB"/>
+    <hyperlink ref="C50" r:id="rId360" tooltip="https://www.amazon.co.uk/dp/B0GQ66CNX6"/>
+    <hyperlink ref="G50" r:id="rId361" tooltip="https://www.amazon.co.uk/stores/Home/page/DE49DE29-7A19-4585-91EF-0BF07D1037EE?lp_asin=B0GQ66CNX6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J50" r:id="rId362" tooltip="https://www.amazon.co.uk/dp/B0GQ66CNX6?psc=1"/>
+    <hyperlink ref="K50" r:id="rId363" tooltip="https://images-na.ssl-images-amazon.com/images/I/71IdvHswVqL._AC_US600_.jpg"/>
+    <hyperlink ref="L50" r:id="rId364" tooltip="https://www.amazon.co.uk/dp/B0GQ66CNX6"/>
+    <hyperlink ref="M50" r:id="rId365" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N50" r:id="rId366"/>
   </hyperlinks>
-  <drawing r:id="rId374"/>
+  <drawing r:id="rId367"/>
 </worksheet>
 </file>
 
@@ -19688,18 +19411,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>15468</v>
+        <v>13361</v>
       </c>
       <c r="C2" s="15">
-        <v>2922756</v>
+        <v>2891172</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>188.95500387897596</v>
+        <v>216.38889304692762</v>
       </c>
       <c r="G2" s="22">
-        <v>0.3217472698907956</v>
+        <v>0.29065871910894536</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19720,7 +19443,7 @@
         <v>297.02728191310206</v>
       </c>
       <c r="G3" s="22">
-        <v>0.06175767030681227</v>
+        <v>0.06458840932822833</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19741,7 +19464,7 @@
         <v>281.4461256304447</v>
       </c>
       <c r="G4" s="22">
-        <v>0.04536661466458659</v>
+        <v>0.047446049425687434</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19762,7 +19485,7 @@
         <v>159.9900442477876</v>
       </c>
       <c r="G5" s="22">
-        <v>0.03760790431617265</v>
+        <v>0.03933170901496694</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19783,7 +19506,7 @@
         <v>69.98992697053639</v>
       </c>
       <c r="G6" s="22">
-        <v>0.08260010400416017</v>
+        <v>0.08638618169161155</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19804,7 +19527,7 @@
         <v>71.97820823244552</v>
       </c>
       <c r="G7" s="22">
-        <v>0.0773166926677067</v>
+        <v>0.08086059867734076</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19825,7 +19548,7 @@
         <v>115.37659963436928</v>
       </c>
       <c r="G8" s="22">
-        <v>0.04551222048881955</v>
+        <v>0.04759832927253742</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19846,7 +19569,7 @@
         <v>56.83162715517241</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0772126885075403</v>
+        <v>0.0807518273581622</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19867,7 +19590,7 @@
         <v>147.94893292682926</v>
       </c>
       <c r="G10" s="22">
-        <v>0.027290691627665106</v>
+        <v>0.02854159415245388</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19888,7 +19611,7 @@
         <v>133.1818181818182</v>
       </c>
       <c r="G11" s="22">
-        <v>0.024024960998439936</v>
+        <v>0.025126174730247128</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19909,7 +19632,7 @@
         <v>69.99027237354086</v>
       </c>
       <c r="G12" s="22">
-        <v>0.03207488299531981</v>
+        <v>0.03354507483466759</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19930,7 +19653,7 @@
         <v>119.98967889908256</v>
       </c>
       <c r="G13" s="22">
-        <v>0.018138325533021322</v>
+        <v>0.01896971806474069</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19951,7 +19674,7 @@
         <v>149.98973305954826</v>
       </c>
       <c r="G14" s="22">
-        <v>0.010130005200208009</v>
+        <v>0.010594326487991646</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19972,7 +19695,7 @@
         <v>71.01993355481727</v>
       </c>
       <c r="G15" s="22">
-        <v>0.018783151326053044</v>
+        <v>0.019644100243647756</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19993,7 +19716,7 @@
         <v>119.98913043478261</v>
       </c>
       <c r="G16" s="22">
-        <v>0.009568382735309413</v>
+        <v>0.010006961364427427</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20014,7 +19737,7 @@
         <v>219.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.004908996359854394</v>
+        <v>0.0051340062652279845</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20035,7 +19758,7 @@
         <v>93.64543524416136</v>
       </c>
       <c r="G18" s="22">
-        <v>0.009797191887675506</v>
+        <v>0.010246258266620258</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20056,7 +19779,7 @@
         <v>59.0</v>
       </c>
       <c r="G19" s="22">
-        <v>0.014581383255330213</v>
+        <v>0.015249738948833972</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20077,7 +19800,7 @@
         <v>89.98976982097187</v>
       </c>
       <c r="G20" s="22">
-        <v>0.008133125325013</v>
+        <v>0.008505917159763314</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20098,7 +19821,7 @@
         <v>99.96845425867508</v>
       </c>
       <c r="G21" s="22">
-        <v>0.006593863754550182</v>
+        <v>0.006896101635920641</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20119,7 +19842,7 @@
         <v>33.9002169197397</v>
       </c>
       <c r="G22" s="22">
-        <v>0.019178367134685386</v>
+        <v>0.02005743125652628</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20140,7 +19863,7 @@
         <v>32.98991031390135</v>
       </c>
       <c r="G23" s="22">
-        <v>0.018554342173686948</v>
+        <v>0.019404803341454925</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20161,7 +19884,7 @@
         <v>89.99079754601227</v>
       </c>
       <c r="G24" s="22">
-        <v>0.006781071242849714</v>
+        <v>0.0070918900104420465</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20182,7 +19905,7 @@
         <v>75.99053627760253</v>
       </c>
       <c r="G25" s="22">
-        <v>0.006593863754550182</v>
+        <v>0.006896101635920641</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20203,7 +19926,7 @@
         <v>89.98913043478261</v>
       </c>
       <c r="G26" s="22">
-        <v>0.003827353094123765</v>
+        <v>0.0040027845457709715</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20224,7 +19947,7 @@
         <v>59.988679245283016</v>
       </c>
       <c r="G27" s="22">
-        <v>0.0055122204888195525</v>
+        <v>0.005764879916463627</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20245,7 +19968,7 @@
         <v>31.97983870967742</v>
       </c>
       <c r="G28" s="22">
-        <v>0.00515860634425377</v>
+        <v>0.005395057431256526</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20266,7 +19989,7 @@
         <v>99.98333333333333</v>
       </c>
       <c r="G29" s="22">
-        <v>0.0012480499219968799</v>
+        <v>0.001305255830142708</v>
       </c>
     </row>
   </sheetData>
@@ -20330,18 +20053,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>25537</v>
+        <v>23430</v>
       </c>
       <c r="C2" s="15">
-        <v>4437029</v>
+        <v>4405445</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>173.74903081802873</v>
+        <v>188.02582159624413</v>
       </c>
       <c r="G2" s="22">
-        <v>0.5311908476339053</v>
+        <v>0.5097024016707274</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20362,7 +20085,7 @@
         <v>307.4000922934933</v>
       </c>
       <c r="G3" s="22">
-        <v>0.045075403016120646</v>
+        <v>0.04714148973198747</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20383,7 +20106,7 @@
         <v>159.9900442477876</v>
       </c>
       <c r="G4" s="22">
-        <v>0.03760790431617265</v>
+        <v>0.03933170901496694</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20404,7 +20127,7 @@
         <v>69.98992697053639</v>
       </c>
       <c r="G5" s="22">
-        <v>0.08260010400416017</v>
+        <v>0.08638618169161155</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20425,7 +20148,7 @@
         <v>71.97820823244552</v>
       </c>
       <c r="G6" s="22">
-        <v>0.0773166926677067</v>
+        <v>0.08086059867734076</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20446,7 +20169,7 @@
         <v>56.83162715517241</v>
       </c>
       <c r="G7" s="22">
-        <v>0.0772126885075403</v>
+        <v>0.0807518273581622</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20467,7 +20190,7 @@
         <v>69.99027237354086</v>
       </c>
       <c r="G8" s="22">
-        <v>0.03207488299531981</v>
+        <v>0.03354507483466759</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20488,7 +20211,7 @@
         <v>119.98967889908256</v>
       </c>
       <c r="G9" s="22">
-        <v>0.018138325533021322</v>
+        <v>0.01896971806474069</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20509,7 +20232,7 @@
         <v>161.4903474903475</v>
       </c>
       <c r="G10" s="22">
-        <v>0.01077483099323973</v>
+        <v>0.011268708666898712</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20530,7 +20253,7 @@
         <v>149.98973305954826</v>
       </c>
       <c r="G11" s="22">
-        <v>0.010130005200208009</v>
+        <v>0.010594326487991646</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20551,7 +20274,7 @@
         <v>159.99132947976878</v>
       </c>
       <c r="G12" s="22">
-        <v>0.00719708788351534</v>
+        <v>0.007526975287156282</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20572,7 +20295,7 @@
         <v>119.98913043478261</v>
       </c>
       <c r="G13" s="22">
-        <v>0.009568382735309413</v>
+        <v>0.010006961364427427</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20593,7 +20316,7 @@
         <v>122.99107142857143</v>
       </c>
       <c r="G14" s="22">
-        <v>0.009318772750910037</v>
+        <v>0.009745910198398886</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20614,7 +20337,7 @@
         <v>89.98976982097187</v>
       </c>
       <c r="G15" s="22">
-        <v>0.008133125325013</v>
+        <v>0.008505917159763314</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20635,7 +20358,7 @@
         <v>99.96845425867508</v>
       </c>
       <c r="G16" s="22">
-        <v>0.006593863754550182</v>
+        <v>0.006896101635920641</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20656,7 +20379,7 @@
         <v>32.98991031390135</v>
       </c>
       <c r="G17" s="22">
-        <v>0.018554342173686948</v>
+        <v>0.019404803341454925</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20677,7 +20400,7 @@
         <v>75.99053627760253</v>
       </c>
       <c r="G18" s="22">
-        <v>0.006593863754550182</v>
+        <v>0.006896101635920641</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20698,7 +20421,7 @@
         <v>59.988679245283016</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0055122204888195525</v>
+        <v>0.005764879916463627</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20719,7 +20442,7 @@
         <v>31.97983870967742</v>
       </c>
       <c r="G20" s="22">
-        <v>0.00515860634425377</v>
+        <v>0.005395057431256526</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20740,7 +20463,7 @@
         <v>99.98333333333333</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0012480499219968799</v>
+        <v>0.001305255830142708</v>
       </c>
     </row>
   </sheetData>
